--- a/artfynd/A 577-2025 artfynd.xlsx
+++ b/artfynd/A 577-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120735199</v>
+        <v>120735187</v>
       </c>
       <c r="B2" t="n">
-        <v>56264</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -754,12 +749,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Även sociala läten</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120735202</v>
+        <v>120735186</v>
       </c>
       <c r="B3" t="n">
-        <v>56259</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,26 +797,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -865,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,15 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120735196</v>
+        <v>120735184</v>
       </c>
       <c r="B4" t="n">
-        <v>56266</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56837</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,7 +922,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -976,17 +966,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Även sociala läten</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 577-2025 artfynd.xlsx
+++ b/artfynd/A 577-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120735187</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120735186</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,8 +1010,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120735184</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>